--- a/data/filtered/china_disaster.xlsx
+++ b/data/filtered/china_disaster.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35267208/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2012-11-29</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6011805/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26266893/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>2010-07-22</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3596502/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>2014-01-03</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20443013/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>1999-12-21</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296874/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>2021-07-09</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35087699/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>2016-11-15</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/22266320/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36421884/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2012-04-18</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3742937/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2019-09-30</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30295905/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>1997-01-03</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304045/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2013-09-30</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10763157/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>2015-07-30</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25956520/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30221757/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>2019-05-31</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25890017/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>2023-08-25</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35192609/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36642518/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>2020-12-18</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26342391/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36459360/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35231370/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>2003-03-01</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2130011/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35497671/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10810268/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>2022-03-25</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26825482/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36789117/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>2012-06-08</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10527288/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>2017-10-14</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5324813/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35215919/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>2008-10-24</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3266407/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>2011-03-08</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5298766/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>2019-09-08</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34800551/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10508894/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/38222804/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/37528113/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3145154/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>2003-09-26</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1438683/</t>
         </is>
@@ -2011,7 +2591,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20431606/</t>
         </is>
@@ -2052,7 +2647,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21948882/</t>
         </is>
@@ -2093,7 +2703,22 @@
           <t>2022-09-15</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295370/</t>
         </is>
@@ -2130,7 +2755,22 @@
           <t>2010-08-04</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5320222/</t>
         </is>
@@ -2171,7 +2811,22 @@
           <t>2019-11-29</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27595272/</t>
         </is>
@@ -2212,7 +2867,22 @@
           <t>2019-12-12</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30357885/</t>
         </is>
@@ -2253,7 +2923,22 @@
           <t>2018-05-12</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27608425/</t>
         </is>
@@ -2294,7 +2979,22 @@
           <t>2021-12-03</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35248741/</t>
         </is>
@@ -2335,7 +3035,22 @@
           <t>2020-10-03</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35176462/</t>
         </is>
@@ -2376,7 +3091,22 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295541/</t>
         </is>
@@ -2417,7 +3147,22 @@
           <t>2023-08-22</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35061128/</t>
         </is>
@@ -2458,7 +3203,22 @@
           <t>2022-08-27</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35496693/</t>
         </is>
@@ -2499,7 +3259,22 @@
           <t>2020-11-27</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34868338/</t>
         </is>
@@ -2540,7 +3315,22 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34807467/</t>
         </is>
@@ -2581,7 +3371,22 @@
           <t>2022-02-24</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35083386/</t>
         </is>
@@ -2622,7 +3427,22 @@
           <t>2021-07-16</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35152517/</t>
         </is>
@@ -2663,7 +3483,22 @@
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35203362/</t>
         </is>
@@ -2704,7 +3539,22 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35256043/</t>
         </is>
@@ -2745,7 +3595,22 @@
           <t>2022-06-09</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35915123/</t>
         </is>
@@ -2786,7 +3651,22 @@
           <t>2020-04-03</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35005710/</t>
         </is>
@@ -2827,7 +3707,22 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35027723/</t>
         </is>
@@ -2868,7 +3763,22 @@
           <t>2022-04-20</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35860951/</t>
         </is>
@@ -2909,7 +3819,22 @@
           <t>2020-09-04</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35196786/</t>
         </is>
@@ -2950,7 +3875,22 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35237993/</t>
         </is>
@@ -2991,7 +3931,22 @@
           <t>2021-12-02</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295114/</t>
         </is>
@@ -3032,7 +3987,22 @@
           <t>2014-03-21</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25715111/</t>
         </is>
@@ -3073,7 +4043,22 @@
           <t>2020-06-16</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35099279/</t>
         </is>
@@ -3114,7 +4099,22 @@
           <t>2014-10-10</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25958914/</t>
         </is>
@@ -3155,7 +4155,22 @@
           <t>2020-02-04</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34954819/</t>
         </is>
